--- a/data/schedule.xlsx
+++ b/data/schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kjhealy/Documents/courses/mptc/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C041841-6795-2645-8EB0-DD8725978DD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B085A3B1-64C5-4A43-B84B-AA56D588B8B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2480" yWindow="2120" windowWidth="23900" windowHeight="18380" xr2:uid="{FF444104-2C96-9340-A7A7-D0D5BB267F7C}"/>
+    <workbookView xWindow="2480" yWindow="3020" windowWidth="28700" windowHeight="17480" xr2:uid="{FF444104-2C96-9340-A7A7-D0D5BB267F7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -120,9 +120,6 @@
     <t>Big Picture: Doing your work properly</t>
   </si>
   <si>
-    <t>The file system; the shell; the terminal</t>
-  </si>
-  <si>
     <t>example</t>
   </si>
   <si>
@@ -135,9 +132,6 @@
     <t>/assignment/01-assignment-quarto-notes</t>
   </si>
   <si>
-    <t>No class (Labor Day)</t>
-  </si>
-  <si>
     <t>Using R to look at data</t>
   </si>
   <si>
@@ -238,6 +232,12 @@
   </si>
   <si>
     <t>Helpers, build systems, and environments</t>
+  </si>
+  <si>
+    <t>Finding data and storing it</t>
+  </si>
+  <si>
+    <t>The shell and the terminal</t>
   </si>
 </sst>
 </file>
@@ -646,7 +646,7 @@
         <v>6</v>
       </c>
       <c r="I1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J1" t="s">
         <v>7</v>
@@ -663,7 +663,7 @@
         <v>11</v>
       </c>
       <c r="C2" s="2">
-        <v>45894</v>
+        <v>46259</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -671,13 +671,13 @@
         <v>27</v>
       </c>
       <c r="H2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="I2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -688,18 +688,18 @@
         <v>12</v>
       </c>
       <c r="C3" s="2">
-        <v>45901</v>
+        <v>46266</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="H3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -710,21 +710,21 @@
         <v>13</v>
       </c>
       <c r="C4" s="2">
-        <v>45908</v>
+        <v>46273</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="H4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="I4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -735,18 +735,18 @@
         <v>14</v>
       </c>
       <c r="C5" s="2">
-        <v>45915</v>
+        <v>46280</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J5" s="3"/>
     </row>
@@ -758,21 +758,21 @@
         <v>15</v>
       </c>
       <c r="C6" s="2">
-        <v>45922</v>
+        <v>46287</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="I6" t="s">
-        <v>45</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -783,18 +783,18 @@
         <v>16</v>
       </c>
       <c r="C7" s="2">
-        <v>45929</v>
+        <v>46294</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I7" t="s">
         <v>49</v>
-      </c>
-      <c r="I7" t="s">
-        <v>51</v>
       </c>
       <c r="J7" s="3"/>
     </row>
@@ -806,18 +806,18 @@
         <v>17</v>
       </c>
       <c r="C8" s="2">
-        <v>45936</v>
+        <v>46301</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H8" t="s">
+        <v>48</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -828,7 +828,7 @@
         <v>18</v>
       </c>
       <c r="C9" s="2">
-        <v>45943</v>
+        <v>46308</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -844,7 +844,7 @@
         <v>19</v>
       </c>
       <c r="C10" s="2">
-        <v>45950</v>
+        <v>46315</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -852,10 +852,10 @@
         <v>26</v>
       </c>
       <c r="H10" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I10" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J10" s="3"/>
     </row>
@@ -867,18 +867,18 @@
         <v>20</v>
       </c>
       <c r="C11" s="2">
-        <v>45957</v>
+        <v>46322</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" t="s">
+        <v>53</v>
+      </c>
+      <c r="H11" t="s">
+        <v>54</v>
+      </c>
+      <c r="I11" t="s">
         <v>55</v>
-      </c>
-      <c r="H11" t="s">
-        <v>56</v>
-      </c>
-      <c r="I11" t="s">
-        <v>57</v>
       </c>
       <c r="J11" s="3"/>
     </row>
@@ -890,21 +890,21 @@
         <v>21</v>
       </c>
       <c r="C12" s="2">
-        <v>45964</v>
+        <v>46329</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H12" t="s">
+        <v>57</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
@@ -915,15 +915,15 @@
         <v>22</v>
       </c>
       <c r="C13" s="2">
-        <v>45971</v>
+        <v>46336</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
@@ -934,18 +934,18 @@
         <v>23</v>
       </c>
       <c r="C14" s="2">
-        <v>45978</v>
+        <v>46343</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
@@ -956,15 +956,15 @@
         <v>24</v>
       </c>
       <c r="C15" s="2">
-        <v>45985</v>
+        <v>46350</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">

--- a/data/schedule.xlsx
+++ b/data/schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kjhealy/Documents/courses/mptc/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B085A3B1-64C5-4A43-B84B-AA56D588B8B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8477315-1F3A-734A-93E2-B0CD85BA9F10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2480" yWindow="3020" windowWidth="28700" windowHeight="17480" xr2:uid="{FF444104-2C96-9340-A7A7-D0D5BB267F7C}"/>
   </bookViews>
@@ -141,9 +141,6 @@
     <t>Tidy data and dplyr</t>
   </si>
   <si>
-    <t>/content/02-content-labor-day</t>
-  </si>
-  <si>
     <t>/example/01-example-oecd</t>
   </si>
   <si>
@@ -238,6 +235,9 @@
   </si>
   <si>
     <t>The shell and the terminal</t>
+  </si>
+  <si>
+    <t>/content/02-content-file-system</t>
   </si>
 </sst>
 </file>
@@ -674,7 +674,7 @@
         <v>30</v>
       </c>
       <c r="I2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>31</v>
@@ -693,13 +693,13 @@
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H3" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -715,16 +715,16 @@
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H4" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" t="s">
         <v>38</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -743,10 +743,10 @@
         <v>32</v>
       </c>
       <c r="H5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J5" s="3"/>
     </row>
@@ -766,13 +766,13 @@
         <v>34</v>
       </c>
       <c r="H6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" t="s">
         <v>42</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -788,13 +788,13 @@
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" t="s">
         <v>46</v>
       </c>
-      <c r="H7" t="s">
-        <v>47</v>
-      </c>
       <c r="I7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J7" s="3"/>
     </row>
@@ -814,10 +814,10 @@
         <v>33</v>
       </c>
       <c r="H8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -852,10 +852,10 @@
         <v>26</v>
       </c>
       <c r="H10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I10" t="s">
         <v>51</v>
-      </c>
-      <c r="I10" t="s">
-        <v>52</v>
       </c>
       <c r="J10" s="3"/>
     </row>
@@ -872,13 +872,13 @@
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" t="s">
+        <v>52</v>
+      </c>
+      <c r="H11" t="s">
         <v>53</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>54</v>
-      </c>
-      <c r="I11" t="s">
-        <v>55</v>
       </c>
       <c r="J11" s="3"/>
     </row>
@@ -898,13 +898,13 @@
         <v>29</v>
       </c>
       <c r="H12" t="s">
+        <v>56</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
@@ -920,10 +920,10 @@
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
@@ -939,13 +939,13 @@
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H14" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
@@ -961,10 +961,10 @@
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">

--- a/data/schedule.xlsx
+++ b/data/schedule.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="66">
   <si>
     <t>group</t>
   </si>
@@ -45,6 +45,9 @@
     <t>date</t>
   </si>
   <si>
+    <t>day2</t>
+  </si>
+  <si>
     <t>date_end</t>
   </si>
   <si>
@@ -57,187 +60,178 @@
     <t>content</t>
   </si>
   <si>
+    <t>example</t>
+  </si>
+  <si>
     <t>assignment</t>
   </si>
   <si>
     <t>note</t>
   </si>
   <si>
-    <t>day2</t>
-  </si>
-  <si>
     <t>Weekly Topics</t>
   </si>
   <si>
     <t>Week 1</t>
   </si>
   <si>
+    <t>Big Picture: Doing your work properly</t>
+  </si>
+  <si>
+    <t>/content/01-content-doing-your-work</t>
+  </si>
+  <si>
+    <t>/example/01-example-oecd</t>
+  </si>
+  <si>
+    <t>/assignment/01-assignment-quarto-notes</t>
+  </si>
+  <si>
     <t>Week 2</t>
   </si>
   <si>
+    <t>The file system and the shell</t>
+  </si>
+  <si>
+    <t>/content/02-content-file-system-and-shell</t>
+  </si>
+  <si>
+    <t>/example/02-example-file-system-and-shell</t>
+  </si>
+  <si>
+    <t>/assignment/02-assignment-find-some-data</t>
+  </si>
+  <si>
     <t>Week 3</t>
   </si>
   <si>
+    <t>Using R to look at data</t>
+  </si>
+  <si>
+    <t>/content/03-content-r-and-ggplot</t>
+  </si>
+  <si>
+    <t>/example/03-example-ggplot</t>
+  </si>
+  <si>
     <t>Week 4</t>
   </si>
   <si>
+    <t>Tidy data and dplyr</t>
+  </si>
+  <si>
+    <t>/content/04-content-dplyr</t>
+  </si>
+  <si>
+    <t>/example/04-example-dplyr</t>
+  </si>
+  <si>
+    <t>/assignment/04-assignment-dplyr</t>
+  </si>
+  <si>
     <t>Week 5</t>
   </si>
   <si>
+    <t>More on dplyr, tidyr, and related packages</t>
+  </si>
+  <si>
+    <t>/content/05-content-dplyr-and-more</t>
+  </si>
+  <si>
+    <t>/example/05-example-dplyr-and-more</t>
+  </si>
+  <si>
     <t>Week 6</t>
   </si>
   <si>
+    <t>Ingesting and cleaning data</t>
+  </si>
+  <si>
+    <t>/content/06-content-ingesting-data</t>
+  </si>
+  <si>
+    <t>/assignment/06-assignment-fars</t>
+  </si>
+  <si>
     <t>Week 7</t>
   </si>
   <si>
+    <t>Version Control: git and GitHub</t>
+  </si>
+  <si>
+    <t>/content/07-content-git</t>
+  </si>
+  <si>
+    <t>/example/07-example-git</t>
+  </si>
+  <si>
     <t>Week 8</t>
   </si>
   <si>
+    <t>No class (Fall break)</t>
+  </si>
+  <si>
     <t>Week 9</t>
   </si>
   <si>
+    <t>Iterating on Data and Models</t>
+  </si>
+  <si>
+    <t>/content/08-content-iteration</t>
+  </si>
+  <si>
+    <t>/example/08-example-iteration</t>
+  </si>
+  <si>
     <t>Week 10</t>
   </si>
   <si>
+    <t>Databases and APIs</t>
+  </si>
+  <si>
+    <t>/content/09-content-databases</t>
+  </si>
+  <si>
+    <t>/example/09-example-databases</t>
+  </si>
+  <si>
+    <t>/assignment/09-assignment-databases</t>
+  </si>
+  <si>
     <t>Week 11</t>
   </si>
   <si>
+    <t>Parallel Computing</t>
+  </si>
+  <si>
+    <t>/content/10-content-parallel</t>
+  </si>
+  <si>
     <t>Week 12</t>
   </si>
   <si>
+    <t>Helpers, build systems, and environments</t>
+  </si>
+  <si>
+    <t>/content/11-content-build</t>
+  </si>
+  <si>
+    <t>/assignment/11-assignment-enchilada</t>
+  </si>
+  <si>
     <t>Week 13</t>
   </si>
   <si>
+    <t>Packages, and LLMs</t>
+  </si>
+  <si>
+    <t>/content/12-content-packages</t>
+  </si>
+  <si>
     <t>Week 14</t>
   </si>
   <si>
-    <t>No class (Fall break)</t>
-  </si>
-  <si>
-    <t>Version Control: git and GitHub</t>
-  </si>
-  <si>
-    <t>Big Picture: Doing your work properly</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Databases and APIs</t>
-  </si>
-  <si>
-    <t>/content/01-content-doing-your-work</t>
-  </si>
-  <si>
-    <t>/assignment/01-assignment-quarto-notes</t>
-  </si>
-  <si>
-    <t>Using R to look at data</t>
-  </si>
-  <si>
-    <t>Ingesting and cleaning data</t>
-  </si>
-  <si>
-    <t>Tidy data and dplyr</t>
-  </si>
-  <si>
-    <t>/example/01-example-oecd</t>
-  </si>
-  <si>
-    <t>/assignment/02-assignment-find-some-data</t>
-  </si>
-  <si>
-    <t>/content/03-content-shell</t>
-  </si>
-  <si>
-    <t>/example/03-example-shell</t>
-  </si>
-  <si>
-    <t>/assignment/03-assignment-shell</t>
-  </si>
-  <si>
-    <t>/content/04-content-r</t>
-  </si>
-  <si>
-    <t>/content/05-content-dplyr</t>
-  </si>
-  <si>
-    <t>/example/05-example-dplyr</t>
-  </si>
-  <si>
-    <t>/assignment/05-assignment-dplyr</t>
-  </si>
-  <si>
-    <t>/example/04-example-ggplot</t>
-  </si>
-  <si>
-    <t>More on dplyr, tidyr, and related packages</t>
-  </si>
-  <si>
-    <t>/content/06-content-dplyr-and-more</t>
-  </si>
-  <si>
-    <t>/content/07-content-ingesting-data</t>
-  </si>
-  <si>
-    <t>/example/06-example-dplyr-and-more</t>
-  </si>
-  <si>
-    <t>/assignment/07-assignment-fars</t>
-  </si>
-  <si>
-    <t>/content/08-content-git</t>
-  </si>
-  <si>
-    <t>/example/08-example-git</t>
-  </si>
-  <si>
-    <t>Iterating on Data and Models</t>
-  </si>
-  <si>
-    <t>/content/09-content-iteration</t>
-  </si>
-  <si>
-    <t>/example/09-example-iteration</t>
-  </si>
-  <si>
-    <t>Parallel Computing</t>
-  </si>
-  <si>
-    <t>/content/10-content-databases</t>
-  </si>
-  <si>
-    <t>/example/10-example-databases</t>
-  </si>
-  <si>
-    <t>/assignment/10-assignment-databases</t>
-  </si>
-  <si>
-    <t>/content/11-content-parallel</t>
-  </si>
-  <si>
-    <t>/content/12-content-build</t>
-  </si>
-  <si>
-    <t>/assignment/12-assignment-enchilada</t>
-  </si>
-  <si>
-    <t>/content/13-content-packages</t>
-  </si>
-  <si>
-    <t>Packages, and LLMs</t>
-  </si>
-  <si>
-    <t>Helpers, build systems, and environments</t>
-  </si>
-  <si>
-    <t>Finding data and storing it</t>
-  </si>
-  <si>
-    <t>The shell and the terminal</t>
-  </si>
-  <si>
-    <t>/content/02-content-file-system</t>
+    <t>TBD</t>
   </si>
 </sst>
 </file>
@@ -608,7 +602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71FE4373-BD3B-FD48-B504-CA3F219CBEF5}">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
@@ -631,36 +625,36 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J1" t="s">
-        <v>7</v>
-      </c>
       <c r="K1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="2">
         <v>46259</v>
@@ -668,24 +662,24 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="I2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C3" s="2">
         <v>46266</v>
@@ -693,21 +687,24 @@
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="H3" t="s">
-        <v>67</v>
+        <v>19</v>
+      </c>
+      <c r="I3" t="s">
+        <v>20</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C4" s="2">
         <v>46273</v>
@@ -715,24 +712,21 @@
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="H4" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="I4" t="s">
-        <v>38</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C5" s="2">
         <v>46280</v>
@@ -740,22 +734,24 @@
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="H5" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I5" t="s">
-        <v>44</v>
-      </c>
-      <c r="J5" s="3"/>
+        <v>29</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C6" s="2">
         <v>46287</v>
@@ -763,24 +759,21 @@
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" t="s">
         <v>34</v>
-      </c>
-      <c r="H6" t="s">
-        <v>41</v>
-      </c>
-      <c r="I6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C7" s="2">
         <v>46294</v>
@@ -788,22 +781,21 @@
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="H7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I7" t="s">
-        <v>48</v>
-      </c>
-      <c r="J7" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="C8" s="2">
         <v>46301</v>
@@ -811,21 +803,21 @@
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H8" t="s">
-        <v>47</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>49</v>
+        <v>41</v>
+      </c>
+      <c r="I8" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="C9" s="2">
         <v>46308</v>
@@ -833,15 +825,15 @@
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="C10" s="2">
         <v>46315</v>
@@ -849,22 +841,21 @@
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="H10" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I10" t="s">
-        <v>51</v>
-      </c>
-      <c r="J10" s="3"/>
+        <v>48</v>
+      </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="C11" s="2">
         <v>46322</v>
@@ -872,22 +863,24 @@
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11" t="s">
+        <v>51</v>
+      </c>
+      <c r="I11" t="s">
         <v>52</v>
       </c>
-      <c r="H11" t="s">
+      <c r="J11" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="I11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J11" s="3"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="C12" s="2">
         <v>46329</v>
@@ -895,24 +888,18 @@
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="H12" t="s">
         <v>56</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>58</v>
-      </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="C13" s="2">
         <v>46336</v>
@@ -920,18 +907,21 @@
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H13" t="s">
         <v>59</v>
       </c>
+      <c r="J13" s="3" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="C14" s="2">
         <v>46343</v>
@@ -939,21 +929,18 @@
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" t="s">
-        <v>64</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="H14" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="C15" s="2">
         <v>46350</v>
@@ -961,27 +948,8 @@
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" t="s">
-        <v>63</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="H18" s="3"/>
+        <v>65</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:C18">

--- a/data/schedule.xlsx
+++ b/data/schedule.xlsx
@@ -120,13 +120,13 @@
     <t>Tidy data and dplyr</t>
   </si>
   <si>
-    <t>/content/04-content-dplyr</t>
+    <t>/content/04-content-r-and-dplyr</t>
   </si>
   <si>
     <t>/example/04-example-dplyr</t>
   </si>
   <si>
-    <t>/assignment/04-assignment-dplyr</t>
+    <t>/assignment/04-assignment-uk-election</t>
   </si>
   <si>
     <t>Week 5</t>

--- a/data/schedule.xlsx
+++ b/data/schedule.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="64">
   <si>
     <t>group</t>
   </si>
@@ -132,37 +132,40 @@
     <t>Week 5</t>
   </si>
   <si>
-    <t>More on dplyr, tidyr, and related packages</t>
-  </si>
-  <si>
-    <t>/content/05-content-dplyr-and-more</t>
-  </si>
-  <si>
-    <t>/example/05-example-dplyr-and-more</t>
+    <t>Tidying, Reshaping, and Ingesting Data</t>
+  </si>
+  <si>
+    <t>/content/05-content-r-tidying-and-ingesting</t>
+  </si>
+  <si>
+    <t>/example/05-example-tidying-and-ingesting</t>
+  </si>
+  <si>
+    <t>/assignment/05-assignment-fars</t>
   </si>
   <si>
     <t>Week 6</t>
   </si>
   <si>
-    <t>Ingesting and cleaning data</t>
-  </si>
-  <si>
-    <t>/content/06-content-ingesting-data</t>
-  </si>
-  <si>
-    <t>/assignment/06-assignment-fars</t>
+    <t>Version Control: git and GitHub</t>
+  </si>
+  <si>
+    <t>/content/06-content-git</t>
+  </si>
+  <si>
+    <t>/example/06-example-git</t>
   </si>
   <si>
     <t>Week 7</t>
   </si>
   <si>
-    <t>Version Control: git and GitHub</t>
-  </si>
-  <si>
-    <t>/content/07-content-git</t>
-  </si>
-  <si>
-    <t>/example/07-example-git</t>
+    <t>Iterating on Data and Models</t>
+  </si>
+  <si>
+    <t>/content/07-content-iteration</t>
+  </si>
+  <si>
+    <t>/example/07-example-iteration</t>
   </si>
   <si>
     <t>Week 8</t>
@@ -174,64 +177,55 @@
     <t>Week 9</t>
   </si>
   <si>
-    <t>Iterating on Data and Models</t>
-  </si>
-  <si>
-    <t>/content/08-content-iteration</t>
-  </si>
-  <si>
-    <t>/example/08-example-iteration</t>
+    <t>Databases and APIs</t>
+  </si>
+  <si>
+    <t>/content/08-content-databases</t>
+  </si>
+  <si>
+    <t>/example/08-example-databases</t>
+  </si>
+  <si>
+    <t>/assignment/08-assignment-databases</t>
   </si>
   <si>
     <t>Week 10</t>
   </si>
   <si>
-    <t>Databases and APIs</t>
-  </si>
-  <si>
-    <t>/content/09-content-databases</t>
-  </si>
-  <si>
-    <t>/example/09-example-databases</t>
-  </si>
-  <si>
-    <t>/assignment/09-assignment-databases</t>
+    <t>Parallel Computing</t>
+  </si>
+  <si>
+    <t>/content/09-content-parallel</t>
   </si>
   <si>
     <t>Week 11</t>
   </si>
   <si>
-    <t>Parallel Computing</t>
-  </si>
-  <si>
-    <t>/content/10-content-parallel</t>
+    <t>Helpers, build systems, and environments</t>
+  </si>
+  <si>
+    <t>/content/10-content-build</t>
+  </si>
+  <si>
+    <t>/assignment/10-assignment-enchilada</t>
   </si>
   <si>
     <t>Week 12</t>
   </si>
   <si>
-    <t>Helpers, build systems, and environments</t>
-  </si>
-  <si>
-    <t>/content/11-content-build</t>
-  </si>
-  <si>
-    <t>/assignment/11-assignment-enchilada</t>
+    <t>Packages, and LLMs</t>
+  </si>
+  <si>
+    <t>/content/11-content-packages</t>
   </si>
   <si>
     <t>Week 13</t>
   </si>
   <si>
-    <t>Packages, and LLMs</t>
-  </si>
-  <si>
-    <t>/content/12-content-packages</t>
+    <t>TBD</t>
   </si>
   <si>
     <t>Week 14</t>
-  </si>
-  <si>
-    <t>TBD</t>
   </si>
 </sst>
 </file>
@@ -767,13 +761,16 @@
       <c r="I6" t="s">
         <v>34</v>
       </c>
+      <c r="J6" s="3" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C7" s="2">
         <v>46294</v>
@@ -781,13 +778,13 @@
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H7" t="s">
-        <v>37</v>
-      </c>
-      <c r="J7" s="3" t="s">
         <v>38</v>
+      </c>
+      <c r="I7" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -795,7 +792,7 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C8" s="2">
         <v>46301</v>
@@ -803,13 +800,13 @@
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -817,7 +814,7 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9" s="2">
         <v>46308</v>
@@ -825,7 +822,7 @@
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
@@ -833,7 +830,7 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C10" s="2">
         <v>46315</v>
@@ -841,13 +838,16 @@
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I10" t="s">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
@@ -855,7 +855,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C11" s="2">
         <v>46322</v>
@@ -863,15 +863,9 @@
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H11" t="s">
-        <v>51</v>
-      </c>
-      <c r="I11" t="s">
-        <v>52</v>
-      </c>
-      <c r="J11" s="3" t="s">
         <v>53</v>
       </c>
     </row>
@@ -893,13 +887,16 @@
       <c r="H12" t="s">
         <v>56</v>
       </c>
+      <c r="J12" s="3" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C13" s="2">
         <v>46336</v>
@@ -907,12 +904,9 @@
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H13" t="s">
-        <v>59</v>
-      </c>
-      <c r="J13" s="3" t="s">
         <v>60</v>
       </c>
     </row>
@@ -931,16 +925,13 @@
       <c r="F14" t="s">
         <v>62</v>
       </c>
-      <c r="H14" t="s">
-        <v>63</v>
-      </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C15" s="2">
         <v>46350</v>
@@ -948,7 +939,7 @@
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/data/schedule.xlsx
+++ b/data/schedule.xlsx
@@ -786,6 +786,11 @@
       <c r="I7" t="s">
         <v>39</v>
       </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>/assignment/06-assignment-cleaning</t>
+        </is>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">

--- a/data/schedule.xlsx
+++ b/data/schedule.xlsx
@@ -1,40 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kjhealy/Documents/courses/mptc/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8477315-1F3A-734A-93E2-B0CD85BA9F10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="2480" yWindow="3020" windowWidth="28700" windowHeight="17480" xr2:uid="{FF444104-2C96-9340-A7A7-D0D5BB267F7C}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="66">
   <si>
     <t>group</t>
   </si>
@@ -156,6 +136,9 @@
     <t>/example/06-example-git</t>
   </si>
   <si>
+    <t>/assignment/06-assignment-cleaning</t>
+  </si>
+  <si>
     <t>Week 7</t>
   </si>
   <si>
@@ -166,6 +149,9 @@
   </si>
   <si>
     <t>/example/07-example-iteration</t>
+  </si>
+  <si>
+    <t>/assignment/07-assignment-iteration</t>
   </si>
   <si>
     <t>Week 8</t>
@@ -231,27 +217,22 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -277,32 +258,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -310,44 +284,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -374,32 +348,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -426,27 +382,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -455,206 +393,222 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71FE4373-BD3B-FD48-B504-CA3F219CBEF5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" style="1"/>
-    <col min="5" max="5" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="62" customWidth="1"/>
-    <col min="8" max="8" width="31.1640625" customWidth="1"/>
-    <col min="9" max="9" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="24.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:11" s="2" customFormat="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>11</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="1">
         <v>46259</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
       <c r="F2" t="s">
         <v>13</v>
       </c>
@@ -664,22 +618,20 @@
       <c r="I2" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="1">
         <v>46266</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
       <c r="F3" t="s">
         <v>18</v>
       </c>
@@ -689,22 +641,20 @@
       <c r="I3" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
         <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="1">
         <v>46273</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
       <c r="F4" t="s">
         <v>23</v>
       </c>
@@ -715,18 +665,16 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="1">
         <v>46280</v>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
       <c r="F5" t="s">
         <v>27</v>
       </c>
@@ -736,22 +684,20 @@
       <c r="I5" t="s">
         <v>29</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
         <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="1">
         <v>46287</v>
       </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
       <c r="F6" t="s">
         <v>32</v>
       </c>
@@ -761,22 +707,20 @@
       <c r="I6" t="s">
         <v>34</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="J6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
         <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="1">
         <v>46294</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
       <c r="F7" t="s">
         <v>37</v>
       </c>
@@ -786,173 +730,153 @@
       <c r="I7" t="s">
         <v>39</v>
       </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>/assignment/06-assignment-cleaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="2">
+        <v>41</v>
+      </c>
+      <c r="C8" s="1">
         <v>46301</v>
       </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
       <c r="F8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+      <c r="J8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="2">
+        <v>46</v>
+      </c>
+      <c r="C9" s="1">
         <v>46308</v>
       </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
       <c r="F9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="2">
+        <v>48</v>
+      </c>
+      <c r="C10" s="1">
         <v>46315</v>
       </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
       <c r="F10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I10" t="s">
-        <v>49</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+      <c r="J10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="2">
+        <v>53</v>
+      </c>
+      <c r="C11" s="1">
         <v>46322</v>
       </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
       <c r="F11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H11" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
-      </c>
-      <c r="C12" s="2">
+        <v>56</v>
+      </c>
+      <c r="C12" s="1">
         <v>46329</v>
       </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
       <c r="F12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H12" t="s">
-        <v>56</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="J12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" t="s">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" s="2">
+        <v>60</v>
+      </c>
+      <c r="C13" s="1">
         <v>46336</v>
       </c>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
       <c r="F13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" t="s">
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
-      </c>
-      <c r="C14" s="2">
+        <v>63</v>
+      </c>
+      <c r="C14" s="1">
         <v>46343</v>
       </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
       <c r="F14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" t="s">
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>63</v>
-      </c>
-      <c r="C15" s="2">
+        <v>65</v>
+      </c>
+      <c r="C15" s="1">
         <v>46350</v>
       </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
       <c r="F15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:C18">
-    <sortCondition ref="C2:C18"/>
-  </sortState>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>